--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484879_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484879_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. VERDEGUER FERRER</t>
+          <t>M. MARTINEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4701</v>
+        <v>7.132</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0313</v>
+        <v>2.6409</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4388</v>
+        <v>4.491</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9313</v>
+        <v>1.1274</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3162</v>
+        <v>0.7943</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6151</v>
+        <v>0.333</v>
       </c>
       <c r="J2" t="n">
-        <v>2.577</v>
+        <v>0.3597</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1786</v>
+        <v>0.2434</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3984</v>
+        <v>0.1163</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6457000000000001</v>
+        <v>0.7677</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8624000000000001</v>
+        <v>0.551</v>
       </c>
       <c r="O2" t="n">
         <v>0.2167</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3774</v>
+        <v>1.5096</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3209</v>
+        <v>1.5096</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9162</v>
+        <v>1.9667</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1526</v>
+        <v>1.036</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7636</v>
+        <v>0.9306</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2452</v>
+        <v>2.5284</v>
       </c>
       <c r="W2" t="n">
         <v>1.2452</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.2832</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. MARTINEZ HERNANDEZ</t>
+          <t>L. VERDEGUER FERRER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.468</v>
+        <v>6.3379</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0563</v>
+        <v>4.4282</v>
       </c>
       <c r="F3" t="n">
-        <v>4.4117</v>
+        <v>1.9097</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1274</v>
+        <v>1.9313</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7943</v>
+        <v>0.3162</v>
       </c>
       <c r="I3" t="n">
-        <v>0.333</v>
+        <v>1.6151</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3597</v>
+        <v>2.577</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2434</v>
+        <v>1.1786</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1163</v>
+        <v>1.3984</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7677</v>
+        <v>-0.6457000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>0.551</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="O3" t="n">
         <v>0.2167</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5096</v>
+        <v>0.3774</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5096</v>
+        <v>1.3209</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3027</v>
+        <v>2.784</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4514</v>
+        <v>1.5495</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8512999999999999</v>
+        <v>1.2345</v>
       </c>
       <c r="V3" t="n">
-        <v>2.5284</v>
+        <v>1.2452</v>
       </c>
       <c r="W3" t="n">
         <v>1.2452</v>
       </c>
       <c r="X3" t="n">
-        <v>1.2832</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. BOSCH ROIG</t>
+          <t>P. SILLA TEBAR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2663</v>
+        <v>6.1181</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6353</v>
+        <v>3.3905</v>
       </c>
       <c r="F4" t="n">
-        <v>2.631</v>
+        <v>2.7276</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2127</v>
+        <v>2.9952</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.6488</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2384</v>
+        <v>2.3464</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8133</v>
+        <v>2.2275</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0729</v>
+        <v>0.2277</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7403</v>
+        <v>1.9998</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3995</v>
+        <v>0.7677</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.09859999999999999</v>
+        <v>0.4211</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4981</v>
+        <v>0.3466</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3774</v>
+        <v>0.1887</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3209</v>
+        <v>1.1322</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7518</v>
+        <v>1.689</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8411999999999999</v>
+        <v>0.8613</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9106</v>
+        <v>0.8277</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9244</v>
+        <v>1.2452</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9244</v>
+        <v>1.2452</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.0716</v>
+        <v>5.3253</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8616</v>
+        <v>2.1153</v>
       </c>
       <c r="F5" t="n">
         <v>3.21</v>
@@ -844,10 +844,10 @@
         <v>1.1322</v>
       </c>
       <c r="S5" t="n">
-        <v>1.7571</v>
+        <v>2.0107</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7947</v>
+        <v>1.0484</v>
       </c>
       <c r="U5" t="n">
         <v>0.9624</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. SILLA TEBAR</t>
+          <t>J. BOSCH ROIG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.8876</v>
+        <v>4.9677</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3187</v>
+        <v>2.3632</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5689</v>
+        <v>2.6046</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9952</v>
+        <v>2.2127</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6488</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3464</v>
+        <v>1.2384</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2275</v>
+        <v>1.8133</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2277</v>
+        <v>1.0729</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9998</v>
+        <v>0.7403</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7677</v>
+        <v>0.3995</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4211</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3466</v>
+        <v>0.4981</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1887</v>
+        <v>0.3774</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1322</v>
+        <v>1.3209</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4585</v>
+        <v>1.4532</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2105</v>
+        <v>0.569</v>
       </c>
       <c r="U6" t="n">
-        <v>0.669</v>
+        <v>0.8842</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2452</v>
+        <v>0.9244</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2452</v>
+        <v>0.9244</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. LICZNAROWSKI</t>
+          <t>J. DALMAU ROIG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.8104</v>
+        <v>3.7025</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5688</v>
+        <v>2.6178</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2416</v>
+        <v>1.0848</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1563</v>
+        <v>3.0922</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5048</v>
+        <v>0.9665</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6516</v>
+        <v>2.1257</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3854</v>
+        <v>3.0555</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1323</v>
+        <v>1.1465</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5177</v>
+        <v>1.909</v>
       </c>
       <c r="M7" t="n">
-        <v>1.5417</v>
+        <v>0.0367</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3725</v>
+        <v>-0.18</v>
       </c>
       <c r="O7" t="n">
-        <v>1.1692</v>
+        <v>0.2167</v>
       </c>
       <c r="P7" t="n">
         <v>0.3774</v>
@@ -1000,28 +1000,28 @@
         <v>1.3209</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3332</v>
+        <v>1.1763</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6525</v>
+        <v>0.2039</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6808</v>
+        <v>0.9724</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9434</v>
+        <v>-0.9434</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2452</v>
+        <v>0.3018</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3018</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MARTIN FERNANDEZ</t>
+          <t>M. LICZNAROWSKI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.7854</v>
+        <v>3.6944</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2416</v>
+        <v>0.4528</v>
       </c>
       <c r="F8" t="n">
-        <v>5.0269</v>
+        <v>3.2416</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2315</v>
+        <v>1.1563</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5017</v>
+        <v>0.5048</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7298</v>
+        <v>0.6516</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6897</v>
+        <v>-0.3854</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8131</v>
+        <v>0.1323</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1234</v>
+        <v>-0.5177</v>
       </c>
       <c r="M8" t="n">
-        <v>1.9212</v>
+        <v>1.5417</v>
       </c>
       <c r="N8" t="n">
-        <v>1.3148</v>
+        <v>0.3725</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6064000000000001</v>
+        <v>1.1692</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7548</v>
+        <v>0.3774</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1322</v>
+        <v>1.3209</v>
       </c>
       <c r="S8" t="n">
-        <v>3.3467</v>
+        <v>1.2173</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3731</v>
+        <v>0.5365</v>
       </c>
       <c r="U8" t="n">
-        <v>1.9735</v>
+        <v>0.6808</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.038</v>
+        <v>0.9434</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.038</v>
+        <v>1.2452</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. DALMAU ROIG</t>
+          <t>H. MARTORELL TRONCHONI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>3.5467</v>
+        <v>3.6211</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3826</v>
+        <v>2.7276</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1641</v>
+        <v>0.8935</v>
       </c>
       <c r="G9" t="n">
-        <v>3.0922</v>
+        <v>2.1722</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9665</v>
+        <v>1.6787</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1257</v>
+        <v>0.4936</v>
       </c>
       <c r="J9" t="n">
-        <v>3.0555</v>
+        <v>1.7286</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1465</v>
+        <v>1.062</v>
       </c>
       <c r="L9" t="n">
-        <v>1.909</v>
+        <v>0.6666</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0367</v>
+        <v>0.4437</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.18</v>
+        <v>0.6167</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2167</v>
+        <v>-0.173</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3774</v>
+        <v>0.5661</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3209</v>
+        <v>0.5661</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0205</v>
+        <v>1.4864</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0312</v>
+        <v>0.999</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0517</v>
+        <v>0.4874</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9434</v>
+        <v>-0.6036</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2452</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. MARTORELL TRONCHONI</t>
+          <t>J. MARTIN FERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>3.4926</v>
+        <v>2.2408</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8637</v>
+        <v>-2.0983</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6289</v>
+        <v>4.3391</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1722</v>
+        <v>1.2315</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6787</v>
+        <v>0.5017</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4936</v>
+        <v>0.7298</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7286</v>
+        <v>-0.6897</v>
       </c>
       <c r="K10" t="n">
-        <v>1.062</v>
+        <v>-0.8131</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6666</v>
+        <v>0.1234</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4437</v>
+        <v>1.9212</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6167</v>
+        <v>1.3148</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.173</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5661</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5661</v>
+        <v>1.1322</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3579</v>
+        <v>1.8021</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1351</v>
+        <v>0.5164</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2228</v>
+        <v>1.2857</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6036</v>
+        <v>-0.038</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.038</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7594</v>
+        <v>-0.9267</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5249</v>
+        <v>-4.0361</v>
       </c>
       <c r="F11" t="n">
-        <v>2.7655</v>
+        <v>3.1094</v>
       </c>
       <c r="G11" t="n">
         <v>-0.5872000000000001</v>
@@ -1312,13 +1312,13 @@
         <v>1.6983</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.04</v>
+        <v>0.7927</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.291</v>
+        <v>0.1978</v>
       </c>
       <c r="U11" t="n">
-        <v>0.251</v>
+        <v>0.595</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.787</v>
+        <v>-2.491</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.7829</v>
+        <v>-3.9632</v>
       </c>
       <c r="F12" t="n">
-        <v>0.996</v>
+        <v>1.4721</v>
       </c>
       <c r="G12" t="n">
         <v>1.5701</v>
@@ -1390,13 +1390,13 @@
         <v>1.6983</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7531</v>
+        <v>0.5429</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8695000000000001</v>
+        <v>-0.0497</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1164</v>
+        <v>0.5926</v>
       </c>
       <c r="V12" t="n">
         <v>-2.5284</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>38.25230000000001</v>
+        <v>39.7221</v>
       </c>
       <c r="E13" t="n">
-        <v>9.168900000000002</v>
+        <v>10.6387</v>
       </c>
       <c r="F13" t="n">
         <v>29.0834</v>
@@ -1450,13 +1450,13 @@
         <v>6.0589</v>
       </c>
       <c r="M13" t="n">
-        <v>7.269800000000001</v>
+        <v>7.2698</v>
       </c>
       <c r="N13" t="n">
         <v>3.1541</v>
       </c>
       <c r="O13" t="n">
-        <v>4.115600000000001</v>
+        <v>4.115599999999999</v>
       </c>
       <c r="P13" t="n">
         <v>-2.8305</v>
@@ -1468,13 +1468,13 @@
         <v>14.1525</v>
       </c>
       <c r="S13" t="n">
-        <v>15.4515</v>
+        <v>16.9213</v>
       </c>
       <c r="T13" t="n">
-        <v>5.9984</v>
+        <v>7.468100000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>9.453099999999999</v>
+        <v>9.453299999999999</v>
       </c>
       <c r="V13" t="n">
         <v>3.9994</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3412</v>
+        <v>1.3676</v>
       </c>
       <c r="E14" t="n">
         <v>1.4049</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0638</v>
+        <v>-0.0373</v>
       </c>
       <c r="G14" t="n">
         <v>1.1936</v>
@@ -1546,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1475</v>
+        <v>0.174</v>
       </c>
       <c r="T14" t="n">
         <v>0.1299</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0176</v>
+        <v>0.0441</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.924</v>
+        <v>0.6823</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.9314</v>
+        <v>-1.2237</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8554</v>
+        <v>1.9059</v>
       </c>
       <c r="G15" t="n">
         <v>-1.6815</v>
@@ -1624,13 +1624,13 @@
         <v>1.887</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6778</v>
+        <v>-0.9195</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5139</v>
+        <v>-0.8062</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1639</v>
+        <v>-0.1134</v>
       </c>
       <c r="V15" t="n">
         <v>1.585</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. TORMO HERRERO</t>
+          <t>J. MAS MICO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.2714</v>
+        <v>-3.3618</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.9606</v>
+        <v>-3.1865</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6892</v>
+        <v>-0.1753</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0397</v>
+        <v>-1.7382</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5885</v>
+        <v>-1.0651</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.6282</v>
+        <v>-0.6731</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.188</v>
+        <v>-1.8019</v>
       </c>
       <c r="K17" t="n">
-        <v>1.094</v>
+        <v>-1.1935</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2821</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8516</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5054999999999999</v>
+        <v>0.1284</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3461</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1887</v>
+        <v>1.5096</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2644</v>
+        <v>-0.1887</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4531</v>
+        <v>1.6983</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.7789</v>
+        <v>-1.5862</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8666</v>
+        <v>-1.1959</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9123</v>
+        <v>-0.3903</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-1.547</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MAS MICO</t>
+          <t>P. TORMO HERRERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.9042</v>
+        <v>-3.3966</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.2839</v>
+        <v>-4.3503</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6203</v>
+        <v>0.9537</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7382</v>
+        <v>-1.0397</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0651</v>
+        <v>0.5885</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6731</v>
+        <v>-1.6282</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.8019</v>
+        <v>-0.188</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.1935</v>
+        <v>1.094</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-1.2821</v>
       </c>
       <c r="M18" t="n">
-        <v>0.06370000000000001</v>
+        <v>-0.8516</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1284</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.3461</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5096</v>
+        <v>0.1887</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1887</v>
+        <v>-2.2644</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6983</v>
+        <v>2.4531</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.1286</v>
+        <v>-1.9041</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2933</v>
+        <v>-1.2563</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8353</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.547</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. FELIZ CAMEAU</t>
+          <t>F. AJAYI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.9957</v>
+        <v>-3.9225</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5829</v>
+        <v>-3.6002</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4128</v>
+        <v>-0.3223</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.9525</v>
+        <v>-1.8121</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6473</v>
+        <v>0.2966</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3051</v>
+        <v>-2.1087</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2979</v>
+        <v>0.903</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1745</v>
+        <v>2.1028</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1234</v>
+        <v>-1.1998</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.2504</v>
+        <v>-2.7151</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.8219</v>
+        <v>-1.8062</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4285</v>
+        <v>-0.9089</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3774</v>
+        <v>0.7548</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2644</v>
+        <v>-2.0757</v>
       </c>
       <c r="R19" t="n">
-        <v>2.6418</v>
+        <v>2.8305</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0998</v>
+        <v>-1.9218</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1634</v>
+        <v>-1.4652</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0636</v>
+        <v>-0.4567</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3208</v>
+        <v>-0.9434</v>
       </c>
       <c r="W19" t="n">
-        <v>1.547</v>
+        <v>-0.9624</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8678</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. AJAYI</t>
+          <t>N. FELIZ CAMEAU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.4361</v>
+        <v>-4.1471</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.6977</v>
+        <v>-1.388</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7383999999999999</v>
+        <v>-2.759</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8121</v>
+        <v>-2.9525</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2966</v>
+        <v>-1.6473</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.1087</v>
+        <v>-1.3051</v>
       </c>
       <c r="J20" t="n">
-        <v>0.903</v>
+        <v>0.2979</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1028</v>
+        <v>0.1745</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1998</v>
+        <v>0.1234</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.7151</v>
+        <v>-3.2504</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.8062</v>
+        <v>-1.8219</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9089</v>
+        <v>-1.4285</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7548</v>
+        <v>0.3774</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0757</v>
+        <v>-2.2644</v>
       </c>
       <c r="R20" t="n">
-        <v>2.8305</v>
+        <v>2.6418</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.4355</v>
+        <v>-1.2512</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.5626</v>
+        <v>-0.9685</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8729</v>
+        <v>-0.2827</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9434</v>
+        <v>-0.3208</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.9624</v>
+        <v>1.547</v>
       </c>
       <c r="X20" t="n">
-        <v>0.019</v>
+        <v>-1.8678</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.9979</v>
+        <v>-4.8258</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4374</v>
+        <v>-2.3399</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5605</v>
+        <v>-2.4859</v>
       </c>
       <c r="G21" t="n">
         <v>-2.9086</v>
@@ -2092,13 +2092,13 @@
         <v>0.7548</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6554</v>
+        <v>-0.4834</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3404</v>
+        <v>-0.243</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3151</v>
+        <v>-0.2404</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2452</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.1624</v>
+        <v>-5.6933</v>
       </c>
       <c r="E22" t="n">
         <v>-5.1405</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0219</v>
+        <v>-0.5528</v>
       </c>
       <c r="G22" t="n">
         <v>-4.3283</v>
@@ -2170,13 +2170,13 @@
         <v>1.1322</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.8341</v>
+        <v>-1.365</v>
       </c>
       <c r="T22" t="n">
         <v>-0.8695000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9646</v>
+        <v>-0.4955</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.823</v>
+        <v>-6.2337</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.1901</v>
+        <v>-4.9952</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6329</v>
+        <v>-1.2385</v>
       </c>
       <c r="G23" t="n">
         <v>-2.9606</v>
@@ -2248,13 +2248,13 @@
         <v>2.2644</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.6171</v>
+        <v>-2.0278</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.6925</v>
+        <v>-1.4976</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9246</v>
+        <v>-0.5302</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3018</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.5439</v>
+        <v>-7.3898</v>
       </c>
       <c r="E24" t="n">
         <v>-4.881</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6628</v>
+        <v>-2.5088</v>
       </c>
       <c r="G24" t="n">
         <v>-4.0212</v>
@@ -2326,13 +2326,13 @@
         <v>1.3209</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.372</v>
+        <v>-2.2179</v>
       </c>
       <c r="T24" t="n">
         <v>-1.281</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.091</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5846</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-38.2524</v>
+        <v>-36.3037</v>
       </c>
       <c r="E25" t="n">
-        <v>-29.0836</v>
+        <v>-29.0834</v>
       </c>
       <c r="F25" t="n">
-        <v>-9.168800000000001</v>
+        <v>-7.220299999999999</v>
       </c>
       <c r="G25" t="n">
         <v>-21.6321</v>
@@ -2404,13 +2404,13 @@
         <v>16.983</v>
       </c>
       <c r="S25" t="n">
-        <v>-15.4517</v>
+        <v>-13.5029</v>
       </c>
       <c r="T25" t="n">
         <v>-9.4533</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.9985</v>
+        <v>-4.0498</v>
       </c>
       <c r="V25" t="n">
         <v>-3.9994</v>
